--- a/ui/src/assets/excel/template.xlsx
+++ b/ui/src/assets/excel/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Marriage-License-System\ui\src\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B209F1EA-4AB5-49EF-8892-4821C60CF3E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E28481F-EF36-434F-9216-AD0032B62FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="1000" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="1000" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="APPLICATION" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="86">
   <si>
     <t>Nueva Vizcaya</t>
   </si>
@@ -265,9 +265,6 @@
     <t>their application for their marriage license.</t>
   </si>
   <si>
-    <t>4Ps ID 025013021-5666-00073</t>
-  </si>
-  <si>
     <t>Subscribed and sworn to before me this</t>
   </si>
   <si>
@@ -287,9 +284,6 @@
   </si>
   <si>
     <t>therefore I/we hereby give you this advice to marry her legally.</t>
-  </si>
-  <si>
-    <t>Solano LGU Employee No. 1999081603</t>
   </si>
   <si>
     <t>therefore I/we hereby give you this advice to marry him legally.</t>
@@ -3515,7 +3509,7 @@
     </row>
     <row r="4" spans="1:35" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F4" s="82" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G4" s="82"/>
       <c r="H4" s="82"/>
@@ -3537,7 +3531,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="88" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H5" s="88"/>
       <c r="I5" s="88"/>
@@ -6504,7 +6498,7 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="83" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B8" s="83"/>
       <c r="C8" s="83"/>
@@ -6920,7 +6914,7 @@
     <row r="7" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="131" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B8" s="131"/>
       <c r="C8" s="131"/>
@@ -7332,7 +7326,7 @@
     </row>
     <row r="19" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -7685,9 +7679,7 @@
       <c r="L29" s="139"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
-      <c r="T29" s="139" t="s">
-        <v>73</v>
-      </c>
+      <c r="T29" s="139"/>
       <c r="U29" s="139"/>
       <c r="V29" s="139"/>
       <c r="W29" s="139"/>
@@ -7946,7 +7938,7 @@
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -7973,7 +7965,7 @@
       <c r="W37" s="132"/>
       <c r="X37" s="132"/>
       <c r="Y37" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Z37" s="1"/>
       <c r="AB37" s="1"/>
@@ -7983,7 +7975,7 @@
     </row>
     <row r="38" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -8531,7 +8523,7 @@
     </row>
     <row r="8" spans="1:35" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="131" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B8" s="131"/>
       <c r="C8" s="131"/>
@@ -8997,7 +8989,7 @@
     </row>
     <row r="19" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -9670,7 +9662,7 @@
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -9697,7 +9689,7 @@
       <c r="W37" s="132"/>
       <c r="X37" s="132"/>
       <c r="Y37" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Z37" s="1"/>
       <c r="AB37" s="1"/>
@@ -9708,7 +9700,7 @@
     </row>
     <row r="38" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -11139,7 +11131,7 @@
     </row>
     <row r="6" spans="1:35" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="131" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B6" s="131"/>
       <c r="C6" s="131"/>
@@ -11594,7 +11586,7 @@
     </row>
     <row r="17" spans="1:35" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -11984,7 +11976,7 @@
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -12011,7 +12003,7 @@
       <c r="W27" s="132"/>
       <c r="X27" s="132"/>
       <c r="Y27" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Z27" s="1"/>
       <c r="AB27" s="1"/>
@@ -12022,7 +12014,7 @@
     </row>
     <row r="28" spans="1:35" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -12368,7 +12360,7 @@
     <row r="38" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="39" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="131" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B39" s="131"/>
       <c r="C39" s="131"/>
@@ -12780,7 +12772,7 @@
     </row>
     <row r="50" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -13148,7 +13140,7 @@
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -13175,7 +13167,7 @@
       <c r="W60" s="132"/>
       <c r="X60" s="132"/>
       <c r="Y60" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Z60" s="1"/>
       <c r="AB60" s="1"/>
@@ -13185,7 +13177,7 @@
     </row>
     <row r="61" spans="1:34" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -13738,7 +13730,7 @@
     </row>
     <row r="10" spans="1:33" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="141" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" s="141"/>
       <c r="C10" s="141"/>
@@ -13910,7 +13902,7 @@
     </row>
     <row r="16" spans="1:33" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T16" s="128">
         <f>+APPLICATION!U8</f>
@@ -13935,7 +13927,7 @@
     </row>
     <row r="17" spans="1:34" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AE17" s="11"/>
       <c r="AF17" s="11"/>
@@ -13943,7 +13935,7 @@
     </row>
     <row r="18" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -14302,7 +14294,7 @@
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
@@ -14857,7 +14849,7 @@
     </row>
     <row r="10" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="141" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" s="141"/>
       <c r="C10" s="141"/>
@@ -15061,7 +15053,7 @@
     </row>
     <row r="16" spans="1:33" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T16" s="128">
         <f>+APPLICATION!B8</f>
@@ -15086,7 +15078,7 @@
     </row>
     <row r="17" spans="1:37" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AE17" s="11"/>
       <c r="AF17" s="11"/>
@@ -15094,7 +15086,7 @@
     </row>
     <row r="18" spans="1:37" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AG18"/>
     </row>
@@ -15360,7 +15352,7 @@
     </row>
     <row r="29" spans="1:37" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C29" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G29" s="37"/>
       <c r="Q29" s="132">
@@ -15799,7 +15791,7 @@
     </row>
     <row r="9" spans="1:34" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="141" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B9" s="141"/>
       <c r="C9" s="141"/>
@@ -15971,7 +15963,7 @@
     </row>
     <row r="15" spans="1:34" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T15" s="146">
         <f>+APPLICATION!U8</f>
@@ -15997,7 +15989,7 @@
     </row>
     <row r="16" spans="1:34" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AE16" s="11"/>
       <c r="AF16" s="11"/>
@@ -16005,7 +15997,7 @@
     </row>
     <row r="17" spans="1:33" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AG17"/>
     </row>
@@ -16199,7 +16191,7 @@
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -16813,7 +16805,7 @@
     </row>
     <row r="44" spans="1:33" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="141" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B44" s="141"/>
       <c r="C44" s="141"/>
@@ -16985,7 +16977,7 @@
     </row>
     <row r="50" spans="1:33" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C50" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T50" s="146">
         <f>+APPLICATION!B8</f>
@@ -17010,7 +17002,7 @@
     </row>
     <row r="51" spans="1:33" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AE51" s="11"/>
       <c r="AF51" s="11"/>
@@ -17018,7 +17010,7 @@
     </row>
     <row r="52" spans="1:33" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AG52"/>
     </row>
@@ -17242,7 +17234,7 @@
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
@@ -17720,7 +17712,7 @@
     <row r="7" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:33" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="141" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B8" s="141"/>
       <c r="C8" s="141"/>
@@ -17892,7 +17884,7 @@
     </row>
     <row r="14" spans="1:33" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T14" s="128">
         <f>+APPLICATION!U8</f>
@@ -17917,7 +17909,7 @@
     </row>
     <row r="15" spans="1:33" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AE15" s="11"/>
       <c r="AF15" s="11"/>
@@ -17925,7 +17917,7 @@
     </row>
     <row r="16" spans="1:33" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AG16"/>
     </row>
@@ -18101,7 +18093,7 @@
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
@@ -18653,7 +18645,7 @@
     </row>
     <row r="40" spans="1:34" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="131" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B40" s="131"/>
       <c r="C40" s="131"/>
@@ -19027,7 +19019,7 @@
     </row>
     <row r="51" spans="1:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -19432,7 +19424,7 @@
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -19459,7 +19451,7 @@
       <c r="W62" s="132"/>
       <c r="X62" s="132"/>
       <c r="Y62" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Z62" s="1"/>
       <c r="AB62" s="1"/>
@@ -19469,7 +19461,7 @@
     </row>
     <row r="63" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -19925,7 +19917,7 @@
     </row>
     <row r="6" spans="1:36" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="131" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B6" s="131"/>
       <c r="C6" s="131"/>
@@ -20301,7 +20293,7 @@
     </row>
     <row r="17" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -20715,7 +20707,7 @@
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -20742,7 +20734,7 @@
       <c r="W28" s="132"/>
       <c r="X28" s="132"/>
       <c r="Y28" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Z28" s="1"/>
       <c r="AA28"/>
@@ -20756,7 +20748,7 @@
     </row>
     <row r="29" spans="1:36" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -21210,7 +21202,7 @@
     </row>
     <row r="41" spans="1:36" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="141" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B41" s="141"/>
       <c r="C41" s="141"/>
@@ -21423,7 +21415,7 @@
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
@@ -21464,7 +21456,7 @@
     </row>
     <row r="48" spans="1:36" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -21501,7 +21493,7 @@
     </row>
     <row r="49" spans="1:33" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -21746,9 +21738,7 @@
       <c r="Q55"/>
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
-      <c r="T55" s="143" t="s">
-        <v>81</v>
-      </c>
+      <c r="T55" s="143"/>
       <c r="U55" s="143"/>
       <c r="V55" s="143"/>
       <c r="W55" s="143"/>
@@ -21800,7 +21790,7 @@
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
